--- a/data/sales_list_sample.xlsx
+++ b/data/sales_list_sample.xlsx
@@ -501,8 +501,6 @@
           <t>三井不動産リアルティ株式会社</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>https://www.mitsui-hanbai.co.jp/inquiry/</t>
@@ -515,13 +513,9 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>サンプル:東京都宅建業者名簿</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>サンプル:宅建業者</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -534,8 +528,6 @@
           <t>住友不動産販売株式会社</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>https://www.stepon.co.jp/contact/</t>
@@ -548,13 +540,9 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>サンプル:東京都宅建業者名簿</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>サンプル:宅建業者</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -567,8 +555,6 @@
           <t>東急リバブル株式会社</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://www.livable.co.jp/inquiry/</t>
@@ -581,13 +567,9 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>サンプル:東京都宅建業者名簿</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>サンプル:宅建業者</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,8 +582,6 @@
           <t>野村不動産ソリューションズ株式会社</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://www.nomu.com/inquiry/</t>
@@ -614,13 +594,9 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>サンプル:東京都宅建業者名簿</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>サンプル:宅建業者</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -633,8 +609,6 @@
           <t>三菱UFJ不動産販売株式会社</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://www.sumai1.com/inquiry/</t>
@@ -647,13 +621,9 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>サンプル:東京都宅建業者名簿</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>サンプル:宅建業者</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -666,8 +636,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -723,6 +706,116 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>エラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>日本司法書士会連合会</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.shiho-shoshi.or.jp/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>サンプル:司法書士</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>東京司法書士会</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.tokyokai.jp/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>サンプル:司法書士</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>日本税理士会連合会</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.nichizeiren.or.jp/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>サンプル:税理士</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>東京弁護士会</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.toben.or.jp/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>サンプル:弁護士</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東京都行政書士会</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.tokyo-gyosei.or.jp/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>サンプル:行政書士</t>
         </is>
       </c>
     </row>
@@ -737,8 +830,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -794,6 +900,116 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>エラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>遺品整理士認定協会</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://ihinseiri.or.jp/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>サンプル:遺品整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>株式会社あんしんネット</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.anshin-net.com/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>サンプル:遺品整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>株式会社メモリーズ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.ihin-memories.jp/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>サンプル:遺品整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>一般社団法人日本相続知財センター</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://chizai-souzoku.jp/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>サンプル:相続コンサル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>税理士法人チェスター</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://chester-tax.com/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>サンプル:相続専門</t>
         </is>
       </c>
     </row>
@@ -808,8 +1024,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -865,6 +1094,116 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>エラー</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>大東建託パートナーズ株式会社</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.kentaku-partners.com/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>サンプル:賃貸管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>スターツピタットハウス株式会社</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.pitathouse.com/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>サンプル:賃貸管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>レオパレス21</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.leopalace21.com/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>サンプル:賃貸管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>三井不動産レジデンシャルリース株式会社</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.mfr.co.jp/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>サンプル:プロパティマネジメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>東急住宅リース株式会社</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.tokyu-housing-lease.co.jp/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>サンプル:プロパティマネジメント</t>
         </is>
       </c>
     </row>
@@ -879,8 +1218,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -938,6 +1290,151 @@
           <t>エラー</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>株式会社保険見直し本舗</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.hokepon.com/</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>サンプル:保険代理店</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>株式会社ほけんの窓口グループ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.hokennomadoguchi.com/</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>サンプル:保険代理店</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ライフプラザパートナーズ株式会社</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.lifeplaza.co.jp/</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>サンプル:生命保険代理店</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>株式会社FPパートナー</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://fp-partner.com/</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>サンプル:生命保険代理店</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>丸紅セーフネット株式会社</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.marubeni-safenet.com/</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>サンプル:損害保険代理店</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
